--- a/output/lancamentos_consolidados.xlsx
+++ b/output/lancamentos_consolidados.xlsx
@@ -414,12 +414,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -427,7 +427,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sicredinvest Automatico</t>
+          <t>Sicredinvest</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -529,21 +529,21 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13657.39</v>
+        <v>1911.82</v>
       </c>
       <c r="J2" t="n">
         <v>591</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sicredinvest Automatico - Pessoa 22</t>
+          <t>Sicredinvest - Pessoa 22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sicredinvest Automatico</t>
+          <t>Sicredinvest</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -582,277 +582,12 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>476.44</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>592</v>
       </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>Sicredinvest Automatico - Pessoa 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sicredinvest Automatico</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Provisao IOF (estorno)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.1.01.03.099</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.1.05.01.003</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4211.81</v>
-      </c>
-      <c r="J4" t="n">
-        <v>593</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Sicredinvest Automatico - Pessoa 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sicredinvest Evolutivo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Rendimento</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.1.01.03.097</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3.1.05.01.002</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1144.73</v>
-      </c>
-      <c r="J5" t="n">
-        <v>591</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Sicredi Evolutivo - Pessoa 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sicredinvest Evolutivo</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Provisao IRRF</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.1.03.04.025</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1.1.01.03.098</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>185.19</v>
-      </c>
-      <c r="J6" t="n">
-        <v>592</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Sicredi Evolutivo - Pessoa 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sicredinvest</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Rendimento</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1.1.01.03.097</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3.1.05.01.002</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1815.66</v>
-      </c>
-      <c r="J7" t="n">
-        <v>591</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Sicredinvest - Pessoa 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sicredinvest</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Provisao IRRF</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.1.03.04.025</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1.1.01.03.098</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>363.14</v>
-      </c>
-      <c r="J8" t="n">
-        <v>592</v>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>Sicredinvest - Pessoa 22</t>
         </is>
@@ -869,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +646,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3342773.31</v>
+        <v>169124.58</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +655,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sicredinvest Automatico</t>
+          <t>Sicredinvest</t>
         </is>
       </c>
     </row>
@@ -936,7 +671,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>900.08</v>
+        <v>22639.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +680,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sicredinvest Automatico</t>
+          <t>Sicredinvest</t>
         </is>
       </c>
     </row>
@@ -961,7 +696,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.15</v>
+        <v>4051.29</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,181 +704,6 @@
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>Sicredinvest Automatico</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1.1.01.03.099 / 1.1.05.01.003</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IOF a Apropriar</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>788.2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sicredinvest Automatico</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1.1.01.03.001</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Aplicacao Financeira Sicredi</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>80785.24000000001</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Sicredinvest Evolutivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1.1.01.03.097</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rendimentos a Apropriar</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>23761.88</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Sicredinvest Evolutivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1.1.01.03.098 / 1.1.03.04.025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IRRF a Apropriar / a Recuperar</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3701.01</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sicredinvest Evolutivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1.1.01.03.001</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Aplicacao Financeira Sicredi</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>169124.58</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Sicredinvest</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1.1.01.03.097</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rendimentos a Apropriar</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>20727.38</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sicredinvest</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1.1.01.03.098 / 1.1.03.04.025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IRRF a Apropriar / a Recuperar</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>4145.47</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Sicredi</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>Sicredinvest</t>
         </is>
